--- a/users.xlsx
+++ b/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.109375" bestFit="1" customWidth="1" min="4" max="5"/>
@@ -477,7 +477,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gAAAAABpyhcIxy-1XLSN2W3-x_X-QFEDwjgrytKKVkr_qLUf6uSB6YBDvdWQdtcUF1tlk5EIWEnBsZRfRJiwT2doryywfSDaig==</t>
+          <t>gAAAAABpyic3OxX0LCXumbNmxxJwTu08qfhpeAm-XQQoVNPBkK3VmGIZymkAO0GHbjOrch3Dhpwy7zIUWxwIG9vAGczVIgoQpQ==</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-30 12:01:21</t>
+          <t>2026-03-31 14:19:01</t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gAAAAABpyha1dUvycaJSgJdsjNx6SSO2_0iVkfz6Ue_MAlAOX9LtrrUshVCglBMhybFqJPyeIySbSGnHT9OKqhYVRHB0bbS6Kg==</t>
+          <t>gAAAAABqq2Wdx56ZL1yVy3UNrowWZrRSQt06TGbtSt9dI-GLU2YOhRW09XYtbH9zqWoPjdpqfB_ZTHGsz5vG3cw6zy7mrXn71Q==</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IFRS</t>
+          <t>CBSL,IFRS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -519,34 +519,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-30 11:52:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>gAAAAABp0H8ydxu2-rVK7ljGXouwjNKhEDi4c_JEXwIw7eHYtbzPG9e7Xrxsxrc7fftZvxkSYMpxwWCVWaU59DHHQnQ8YVSV4w==</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>gAAAAABp0H8yhxnI1OZtmgWkrT4Tq_VZynVuS_PhyIdYnYyI8TyFPbGMnwv37qJEGUujSD_pYmD-J_L3esnUyCLEab57sVk5aA==</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CBSL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-04 08:32:10</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-04-04 08:32:10</t>
+          <t>2026-09-17 09:29:25</t>
         </is>
       </c>
     </row>
